--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.51628773928216</v>
+        <v>7.396396757633351</v>
       </c>
       <c r="D2" t="n">
-        <v>52.15136114106779</v>
+        <v>8.474596185423517</v>
       </c>
       <c r="E2" t="n">
-        <v>9.78634661875248</v>
+        <v>1.590281325547278</v>
       </c>
       <c r="F2" t="n">
-        <v>12.50416822443876</v>
+        <v>2.031927336471299</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.48852062695277</v>
+        <v>8.204384601879825</v>
       </c>
       <c r="D3" t="n">
-        <v>35.36240942017385</v>
+        <v>5.746391530778251</v>
       </c>
       <c r="E3" t="n">
-        <v>9.78634661875248</v>
+        <v>1.590281325547278</v>
       </c>
       <c r="F3" t="n">
-        <v>12.50416822443876</v>
+        <v>2.031927336471299</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.98012834267828</v>
+        <v>8.771770855685221</v>
       </c>
       <c r="D4" t="n">
-        <v>53.53271474919508</v>
+        <v>8.699066146744201</v>
       </c>
       <c r="E4" t="n">
-        <v>9.78634661875248</v>
+        <v>1.590281325547278</v>
       </c>
       <c r="F4" t="n">
-        <v>12.50416822443876</v>
+        <v>2.031927336471299</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>71.50177307100574</v>
+        <v>11.61903812403843</v>
       </c>
       <c r="D5" t="n">
-        <v>70.70153076815522</v>
+        <v>11.48899874982522</v>
       </c>
       <c r="E5" t="n">
-        <v>9.78634661875248</v>
+        <v>1.590281325547278</v>
       </c>
       <c r="F5" t="n">
-        <v>12.50416822443876</v>
+        <v>2.031927336471299</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
